--- a/etf_holdings/2026-08-27_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:56</t>
+          <t>2026-08-27 17:13:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.90%11,884,000</t>
+          <t>9.87%11,884,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.90%</t>
+          <t>9.87%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:56</t>
+          <t>2026-08-27 17:13:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,20 +583,20 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.85%4,843,000</t>
+          <t>9.11%4,807,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.85%</t>
+          <t>9.11%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4843000</v>
+        <v>4807000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:56</t>
+          <t>2026-08-27 17:13:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.12%20,300,000</t>
+          <t>8.25%20,300,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.12%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:56</t>
+          <t>2026-08-27 17:13:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.03%3865</t>
+          <t>+5.86%3340</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.03%</t>
+          <t>+5.86%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3865</v>
+        <v>3340</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.01%5,148,000</t>
+          <t>6.88%5,979,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.01%</t>
+          <t>6.88%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5148000</v>
+        <v>5979000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:56</t>
+          <t>2026-08-27 17:13:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+5.86%3340</t>
+          <t>-2.03%3865</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>-2.03%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3340</v>
+        <v>3865</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.51%5,979,000</t>
+          <t>6.85%5,148,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.51%</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5979000</v>
+        <v>5148000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:56</t>
+          <t>2026-08-27 17:13:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.21%2,226,000</t>
+          <t>5.23%2,226,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.21%</t>
+          <t>5.23%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:56</t>
+          <t>2026-08-27 17:13:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.4%5645</t>
+          <t>+3.35%555</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+3.35%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5645</v>
+        <v>555</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.75%2,407,000</t>
+          <t>4.85%25,387,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>4.85%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2407000</v>
+        <v>25387000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:56</t>
+          <t>2026-08-27 17:13:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+3.35%555</t>
+          <t>+1.7%2090</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+3.35%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>555</v>
+        <v>2090</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.70%25,387,000</t>
+          <t>4.73%6,564,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.70%</t>
+          <t>4.73%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>25387000</v>
+        <v>6564000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:56</t>
+          <t>2026-08-27 17:13:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.7%2090</t>
+          <t>-1.4%5645</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2090</v>
+        <v>5645</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.65%6,564,000</t>
+          <t>4.68%2,407,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.65%</t>
+          <t>4.68%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6564000</v>
+        <v>2407000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:56</t>
+          <t>2026-08-27 17:13:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.99%5090</t>
+          <t>+1.14%1770</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5090</v>
+        <v>1770</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.32%2,486,000</t>
+          <t>4.42%7,250,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.42%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2486000</v>
+        <v>7250000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:56</t>
+          <t>2026-08-27 17:13:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.14%1770</t>
+          <t>+0.99%5090</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1770</v>
+        <v>5090</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.25%7,040,000</t>
+          <t>4.36%2,486,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>4.36%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>7040000</v>
+        <v>2486000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:56</t>
+          <t>2026-08-27 17:13:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+2.2%605</t>
+          <t>+9.75%1295</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+9.75%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>605</v>
+        <v>1295</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.98%19,479,000</t>
+          <t>4.29%9,624,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.98%</t>
+          <t>4.29%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>19479000</v>
+        <v>9624000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:56</t>
+          <t>2026-08-27 17:13:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+9.75%1295</t>
+          <t>+2.2%605</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+9.75%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1295</v>
+        <v>605</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.92%9,624,000</t>
+          <t>4.06%19,479,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>4.06%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>9624000</v>
+        <v>19479000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:56</t>
+          <t>2026-08-27 17:13:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.81%89,518,000</t>
+          <t>3.65%89,518,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.81%</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:56</t>
+          <t>2026-08-27 17:13:16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.23%4,671,848</t>
+          <t>3.31%4,671,848</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.31%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:57</t>
+          <t>2026-08-27 17:13:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.90%5,498,000</t>
+          <t>2.74%5,498,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.74%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:57</t>
+          <t>2026-08-27 17:13:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1502,16 +1502,16 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.08%383,900</t>
+          <t>1.80%341,900</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>383900</v>
+        <v>341900</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:57</t>
+          <t>2026-08-27 17:13:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.58%2,264,000</t>
+          <t>1.74%2,264,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:57</t>
+          <t>2026-08-27 17:13:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1628,16 +1628,16 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.95%11,275,450</t>
+          <t>1.00%11,775,450</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>11275450</v>
+        <v>11775450</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:57</t>
+          <t>2026-08-27 17:13:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.83%2,477,000</t>
+          <t>0.82%2,477,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:57</t>
+          <t>2026-08-27 17:13:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.70%1,957,000</t>
+          <t>0.69%1,957,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:57</t>
+          <t>2026-08-27 17:13:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1797,40 +1797,40 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>4979華星光</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-3.35%5920</t>
+          <t>+3.18%617</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.35%</t>
+          <t>+3.18%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>617</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.69%325,000</t>
+          <t>0.67%3,173,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>325000</v>
+        <v>3173000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:57</t>
+          <t>2026-08-27 17:13:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1860,40 +1860,40 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+9.62%1310</t>
+          <t>-3.35%5920</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+9.62%</t>
+          <t>-3.35%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.54%1,301,000</t>
+          <t>0.66%325,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1301000</v>
+        <v>325000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:57</t>
+          <t>2026-08-27 17:13:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1923,40 +1923,40 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4979華星光</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+3.18%617</t>
+          <t>+9.62%1310</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+3.18%</t>
+          <t>+9.62%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.50%2,424,000</t>
+          <t>0.59%1,301,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>2424000</v>
+        <v>1301000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:57</t>
+          <t>2026-08-27 17:13:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.44%5,917,000</t>
+          <t>0.45%5,917,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:57</t>
+          <t>2026-08-27 17:13:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.43%477,000</t>
+          <t>0.45%477,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:57</t>
+          <t>2026-08-27 17:13:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.26%1,645,000</t>
+          <t>0.27%1,645,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:57</t>
+          <t>2026-08-27 17:13:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2195,12 +2195,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.22%3,249,000</t>
+          <t>0.23%3,249,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:57</t>
+          <t>2026-08-27 17:13:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2238,40 +2238,40 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>6271同欣電</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+10%1430</t>
+          <t>+0.96%210</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.22%483,000</t>
+          <t>0.16%2,223,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>483000</v>
+        <v>2223000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:58</t>
+          <t>2026-08-27 17:13:22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2301,38 +2301,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6271同欣電</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.96%210</t>
+          <t>+10%1430</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>210</v>
+        <v>1430</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.16%2,223,000</t>
+          <t>0.14%283,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>2223000</v>
+        <v>283000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:58</t>
+          <t>2026-08-27 17:13:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.12%1,741,000</t>
+          <t>0.13%1,741,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:58</t>
+          <t>2026-08-27 17:13:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:58</t>
+          <t>2026-08-27 17:13:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:58</t>
+          <t>2026-08-27 17:13:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:58</t>
+          <t>2026-08-27 17:13:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:58</t>
+          <t>2026-08-27 17:13:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:58</t>
+          <t>2026-08-27 17:13:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:58</t>
+          <t>2026-08-27 17:13:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:58</t>
+          <t>2026-08-27 17:13:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:58</t>
+          <t>2026-08-27 17:13:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:58</t>
+          <t>2026-08-27 17:13:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:58</t>
+          <t>2026-08-27 17:13:22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:58</t>
+          <t>2026-08-27 17:13:22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-27 16:38:58</t>
+          <t>2026-08-27 17:13:22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:00</t>
+          <t>2026-08-27 17:13:23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:00</t>
+          <t>2026-08-27 17:13:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:00</t>
+          <t>2026-08-27 17:13:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:00</t>
+          <t>2026-08-27 17:13:23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:00</t>
+          <t>2026-08-27 17:13:23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-27 16:39:00</t>
+          <t>2026-08-27 17:13:23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-27_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:16</t>
+          <t>2026-08-27 19:37:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:16</t>
+          <t>2026-08-27 19:37:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:16</t>
+          <t>2026-08-27 19:37:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:16</t>
+          <t>2026-08-27 19:37:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:16</t>
+          <t>2026-08-27 19:37:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:16</t>
+          <t>2026-08-27 19:37:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:16</t>
+          <t>2026-08-27 19:37:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:16</t>
+          <t>2026-08-27 19:37:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:16</t>
+          <t>2026-08-27 19:37:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:16</t>
+          <t>2026-08-27 19:37:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:16</t>
+          <t>2026-08-27 19:37:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:16</t>
+          <t>2026-08-27 19:37:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:16</t>
+          <t>2026-08-27 19:37:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:16</t>
+          <t>2026-08-27 19:37:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:16</t>
+          <t>2026-08-27 19:37:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:20</t>
+          <t>2026-08-27 19:37:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:20</t>
+          <t>2026-08-27 19:37:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:20</t>
+          <t>2026-08-27 19:37:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:20</t>
+          <t>2026-08-27 19:37:15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:20</t>
+          <t>2026-08-27 19:37:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:20</t>
+          <t>2026-08-27 19:37:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:20</t>
+          <t>2026-08-27 19:37:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:20</t>
+          <t>2026-08-27 19:37:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:20</t>
+          <t>2026-08-27 19:37:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:20</t>
+          <t>2026-08-27 19:37:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:20</t>
+          <t>2026-08-27 19:37:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:20</t>
+          <t>2026-08-27 19:37:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:20</t>
+          <t>2026-08-27 19:37:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:20</t>
+          <t>2026-08-27 19:37:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:22</t>
+          <t>2026-08-27 19:37:17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:22</t>
+          <t>2026-08-27 19:37:17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:22</t>
+          <t>2026-08-27 19:37:17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:22</t>
+          <t>2026-08-27 19:37:17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:22</t>
+          <t>2026-08-27 19:37:17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:22</t>
+          <t>2026-08-27 19:37:17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:22</t>
+          <t>2026-08-27 19:37:17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:22</t>
+          <t>2026-08-27 19:37:17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:22</t>
+          <t>2026-08-27 19:37:17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:22</t>
+          <t>2026-08-27 19:37:17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:22</t>
+          <t>2026-08-27 19:37:17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:22</t>
+          <t>2026-08-27 19:37:17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:22</t>
+          <t>2026-08-27 19:37:17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:22</t>
+          <t>2026-08-27 19:37:17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:22</t>
+          <t>2026-08-27 19:37:17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:23</t>
+          <t>2026-08-27 19:37:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:23</t>
+          <t>2026-08-27 19:37:18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:23</t>
+          <t>2026-08-27 19:37:18</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:23</t>
+          <t>2026-08-27 19:37:18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:23</t>
+          <t>2026-08-27 19:37:18</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-27 17:13:23</t>
+          <t>2026-08-27 19:37:18</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-27_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-27_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:10</t>
+          <t>2026-08-27 22:47:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:10</t>
+          <t>2026-08-27 22:47:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:10</t>
+          <t>2026-08-27 22:47:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:10</t>
+          <t>2026-08-27 22:47:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:10</t>
+          <t>2026-08-27 22:47:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:10</t>
+          <t>2026-08-27 22:47:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:10</t>
+          <t>2026-08-27 22:47:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:10</t>
+          <t>2026-08-27 22:47:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:10</t>
+          <t>2026-08-27 22:47:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:10</t>
+          <t>2026-08-27 22:47:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:10</t>
+          <t>2026-08-27 22:47:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:10</t>
+          <t>2026-08-27 22:47:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:10</t>
+          <t>2026-08-27 22:47:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:10</t>
+          <t>2026-08-27 22:47:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:10</t>
+          <t>2026-08-27 22:47:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:15</t>
+          <t>2026-08-27 22:47:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:15</t>
+          <t>2026-08-27 22:47:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:15</t>
+          <t>2026-08-27 22:47:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:15</t>
+          <t>2026-08-27 22:47:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:15</t>
+          <t>2026-08-27 22:47:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:15</t>
+          <t>2026-08-27 22:47:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:15</t>
+          <t>2026-08-27 22:47:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:15</t>
+          <t>2026-08-27 22:47:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:15</t>
+          <t>2026-08-27 22:47:43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:15</t>
+          <t>2026-08-27 22:47:43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:15</t>
+          <t>2026-08-27 22:47:43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:15</t>
+          <t>2026-08-27 22:47:43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:15</t>
+          <t>2026-08-27 22:47:43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:15</t>
+          <t>2026-08-27 22:47:43</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:17</t>
+          <t>2026-08-27 22:47:44</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:17</t>
+          <t>2026-08-27 22:47:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:17</t>
+          <t>2026-08-27 22:47:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:17</t>
+          <t>2026-08-27 22:47:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:17</t>
+          <t>2026-08-27 22:47:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:17</t>
+          <t>2026-08-27 22:47:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:17</t>
+          <t>2026-08-27 22:47:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:17</t>
+          <t>2026-08-27 22:47:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:17</t>
+          <t>2026-08-27 22:47:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:17</t>
+          <t>2026-08-27 22:47:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:17</t>
+          <t>2026-08-27 22:47:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:17</t>
+          <t>2026-08-27 22:47:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:17</t>
+          <t>2026-08-27 22:47:44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:17</t>
+          <t>2026-08-27 22:47:44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:17</t>
+          <t>2026-08-27 22:47:44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:18</t>
+          <t>2026-08-27 22:47:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:18</t>
+          <t>2026-08-27 22:47:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:18</t>
+          <t>2026-08-27 22:47:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:18</t>
+          <t>2026-08-27 22:47:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:18</t>
+          <t>2026-08-27 22:47:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-27 19:37:18</t>
+          <t>2026-08-27 22:47:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
